--- a/templates/ModeloSolicitacaoMob.xlsx
+++ b/templates/ModeloSolicitacaoMob.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://vestas-my.sharepoint.com/personal/sapsd_vestas_com/Documents/Documents/GIT/SolicitadorMobilizacao-BR4/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="499" documentId="13_ncr:1_{0F2B1A9E-51FF-41E1-905E-9E16B83A400A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FF9369F3-59F5-4AD4-B428-E62D07BDEF7D}"/>
+  <xr:revisionPtr revIDLastSave="664" documentId="13_ncr:1_{0F2B1A9E-51FF-41E1-905E-9E16B83A400A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0C7E4402-7CAD-4C88-BD34-3BE947FF6AD9}"/>
   <bookViews>
     <workbookView xWindow="-11535" yWindow="-21720" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/templates/ModeloSolicitacaoMob.xlsx
+++ b/templates/ModeloSolicitacaoMob.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://vestas-my.sharepoint.com/personal/sapsd_vestas_com/Documents/Documents/GIT/SolicitadorMobilizacao-BR4/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="664" documentId="13_ncr:1_{0F2B1A9E-51FF-41E1-905E-9E16B83A400A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0C7E4402-7CAD-4C88-BD34-3BE947FF6AD9}"/>
+  <xr:revisionPtr revIDLastSave="665" documentId="13_ncr:1_{0F2B1A9E-51FF-41E1-905E-9E16B83A400A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BADE16AB-A797-50BE-9DC6-4F41C0FAD9B6}"/>
   <bookViews>
     <workbookView xWindow="-11535" yWindow="-21720" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/templates/ModeloSolicitacaoMob.xlsx
+++ b/templates/ModeloSolicitacaoMob.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://vestas-my.sharepoint.com/personal/sapsd_vestas_com/Documents/Documents/GIT/SolicitadorMobilizacao-BR4/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="665" documentId="13_ncr:1_{0F2B1A9E-51FF-41E1-905E-9E16B83A400A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BADE16AB-A797-50BE-9DC6-4F41C0FAD9B6}"/>
+  <xr:revisionPtr revIDLastSave="664" documentId="13_ncr:1_{0F2B1A9E-51FF-41E1-905E-9E16B83A400A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FBE0AE5A-8A3B-4044-8533-2AE23BEA4A64}"/>
   <bookViews>
     <workbookView xWindow="-11535" yWindow="-21720" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1118,10 +1118,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
